--- a/etf_holdings/2026-09-02_common_holdings_all.xlsx
+++ b/etf_holdings/2026-09-02_common_holdings_all.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>8.97%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13.58%</t>
+          <t>13.51%</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -779,11 +779,11 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>8.84%</t>
+          <t>8.39%</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>378000</v>
+        <v>363000</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -800,12 +800,12 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>103.56%</t>
+          <t>103.05%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>8.63%</t>
+          <t>8.59%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -900,11 +900,11 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>47000</v>
+        <v>52000</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -965,11 +965,11 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>5.68%</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>114000</v>
+        <v>106000</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -986,12 +986,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>60.72%</t>
+          <t>60.66%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>5.05%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>56.94%</t>
+          <t>57.82%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1337,11 +1337,11 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>151000</v>
+        <v>140000</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>37.24%</t>
+          <t>37.49%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">

--- a/etf_holdings/2026-09-02_common_holdings_all.xlsx
+++ b/etf_holdings/2026-09-02_common_holdings_all.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.23%</t>
+          <t>9.31%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -662,7 +662,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11.19%</t>
+          <t>11.23%</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8.26%</t>
+          <t>8.27%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -701,11 +701,11 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>15.86%</t>
+          <t>15.59%</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>10800000</v>
+        <v>10500000</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>6.24%</t>
+          <t>6.22%</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -792,7 +792,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.58%</t>
+          <t>8.55%</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -800,12 +800,12 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>103.05%</t>
+          <t>102.88%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>8.59%</t>
+          <t>8.57%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -835,11 +835,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.21%</t>
+          <t>9.17%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4757000</v>
+        <v>4750000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.39%</t>
+          <t>9.31%</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -874,11 +874,11 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>317000</v>
+        <v>315000</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -986,12 +986,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>60.66%</t>
+          <t>60.35%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>5.03%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.54%</t>
+          <t>7.71%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.77%</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1060,11 +1060,11 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.08%</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>742000</v>
+        <v>736000</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>5.48%</t>
+          <t>5.62%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>7.31%</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>6.90%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>57.82%</t>
+          <t>58.53%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1220,11 +1220,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1600000</v>
+        <v>1450000</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1246,11 +1246,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>627000</v>
+        <v>621000</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>37.49%</t>
+          <t>37.00%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
